--- a/data/trans_dic/P1404-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P1404-Edad-trans_dic.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,75</t>
+          <t>0,17; 1,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,4</t>
+          <t>0,0; 1,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -737,42 +737,42 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,23</t>
+          <t>0,0; 1,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,46</t>
+          <t>0,0; 1,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,25</t>
+          <t>0,0; 1,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,33; 4,47</t>
+          <t>0,3; 4,29</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,11</t>
+          <t>0,21; 1,18</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,75</t>
+          <t>0,0; 0,87</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,83</t>
+          <t>0,0; 0,93</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,15; 2,17</t>
+          <t>0,14; 1,93</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,52</t>
+          <t>0,25; 1,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,33; 4,02</t>
+          <t>1,28; 3,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,9</t>
+          <t>1,09; 3,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,16</t>
+          <t>0,29; 3,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,15</t>
+          <t>0,83; 2,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,7</t>
+          <t>0,6; 2,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,88</t>
+          <t>0,82; 2,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,81</t>
+          <t>1,09; 3,78</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 1,89</t>
+          <t>0,66; 1,78</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,12; 2,72</t>
+          <t>1,18; 2,87</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,18; 2,89</t>
+          <t>1,19; 2,86</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,85</t>
+          <t>0,95; 2,8</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,95; 6,34</t>
+          <t>2,82; 6,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,25; 8,0</t>
+          <t>4,05; 8,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,05; 6,71</t>
+          <t>3,01; 6,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,32; 7,23</t>
+          <t>3,39; 7,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,42; 5,31</t>
+          <t>2,29; 5,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,62; 5,5</t>
+          <t>2,57; 5,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,59; 4,09</t>
+          <t>1,71; 4,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,21</t>
+          <t>1,1; 2,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,94; 5,06</t>
+          <t>3,03; 5,28</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,82; 6,06</t>
+          <t>3,82; 6,2</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,69; 4,76</t>
+          <t>2,78; 4,97</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 4,35</t>
+          <t>2,5; 4,65</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,27 +1104,27 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
+          <t>10,03%</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>9,25%</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>10,79%</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
           <t>10,35%</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>9,25%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>10,79%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>10,35%</t>
-        </is>
-      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>11,85%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,92; 13,18</t>
+          <t>7,71; 13,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,03; 12,1</t>
+          <t>6,84; 11,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,73; 12,7</t>
+          <t>8,01; 12,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,37; 14,57</t>
+          <t>11,21; 16,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,19; 10,8</t>
+          <t>6,03; 10,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,8; 15,68</t>
+          <t>9,78; 15,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,47; 13,2</t>
+          <t>8,5; 13,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,15; 12,87</t>
+          <t>8,46; 11,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,53; 11,2</t>
+          <t>7,55; 11,28</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,03; 12,7</t>
+          <t>9,03; 12,69</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,62; 12,07</t>
+          <t>8,8; 12,16</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,87; 12,42</t>
+          <t>10,31; 13,54</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>23,98%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>14,28; 21,77</t>
+          <t>14,05; 22,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,69; 23,48</t>
+          <t>15,74; 23,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,56; 24,28</t>
+          <t>16,25; 24,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20,73; 27,56</t>
+          <t>19,78; 26,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,47; 25,78</t>
+          <t>16,82; 25,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,81; 30,25</t>
+          <t>21,52; 30,23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,9; 28,62</t>
+          <t>20,18; 28,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>22,28; 27,61</t>
+          <t>22,27; 28,02</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16,84; 22,21</t>
+          <t>16,97; 22,66</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19,76; 25,56</t>
+          <t>19,79; 25,64</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19,31; 24,74</t>
+          <t>18,96; 24,65</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,25; 26,55</t>
+          <t>21,99; 26,29</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>32,73%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15,66; 24,78</t>
+          <t>15,39; 24,16</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>30,86; 42,26</t>
+          <t>30,8; 42,52</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26,37; 36,36</t>
+          <t>26,76; 36,63</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26,29; 34,06</t>
+          <t>25,98; 33,55</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>23,55; 32,88</t>
+          <t>23,61; 33,12</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29,91; 39,77</t>
+          <t>29,77; 40,37</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26,54; 36,49</t>
+          <t>26,33; 35,88</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>34,11; 82,88</t>
+          <t>32,17; 38,65</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20,84; 27,45</t>
+          <t>21,25; 27,3</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>31,95; 40,02</t>
+          <t>31,65; 39,55</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>28,12; 35,08</t>
+          <t>28,04; 34,76</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>32,21; 72,68</t>
+          <t>30,35; 35,45</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,52%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16,02; 27,05</t>
+          <t>15,69; 27,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>26,66; 40,17</t>
+          <t>26,62; 39,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26,17; 36,67</t>
+          <t>26,42; 36,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32,1; 41,22</t>
+          <t>31,84; 40,84</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>20,85; 31,22</t>
+          <t>21,1; 31,5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,49; 40,81</t>
+          <t>30,5; 40,22</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,6; 39,25</t>
+          <t>28,91; 39,87</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>38,98; 45,24</t>
+          <t>38,3; 45,1</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>20,44; 27,72</t>
+          <t>20,69; 28,13</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30,42; 37,76</t>
+          <t>30,49; 38,51</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29,37; 36,73</t>
+          <t>29,06; 36,72</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>37,13; 42,66</t>
+          <t>36,9; 42,43</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>15,26%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,02; 8,9</t>
+          <t>6,95; 8,88</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10,2; 12,53</t>
+          <t>10,26; 12,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10,41; 12,58</t>
+          <t>10,41; 12,51</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10,6; 14,93</t>
+          <t>13,3; 15,62</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,25; 11,4</t>
+          <t>9,24; 11,34</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,61; 15,0</t>
+          <t>12,56; 14,97</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,1; 14,5</t>
+          <t>12,06; 14,51</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>15,67; 35,12</t>
+          <t>15,14; 17,0</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8,44; 9,89</t>
+          <t>8,45; 9,83</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11,79; 13,39</t>
+          <t>11,77; 13,4</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11,56; 13,19</t>
+          <t>11,48; 13,19</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>14,35; 27,09</t>
+          <t>14,56; 15,99</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4935</t>
+          <t>5361</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4935</t>
+          <t>5361</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>926; 8622</t>
+          <t>855; 8872</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5893</t>
+          <t>0; 5254</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2088,42 +2088,42 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5768</t>
+          <t>0; 6406</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 6273</t>
+          <t>0; 5844</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4951</t>
+          <t>0; 4477</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1046; 14014</t>
+          <t>1106; 15546</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1782; 10689</t>
+          <t>1995; 11376</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 6636</t>
+          <t>0; 7690</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 6765</t>
+          <t>0; 7555</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1104; 15471</t>
+          <t>1110; 14834</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5342</t>
+          <t>5931</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10520</t>
+          <t>10563</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15862</t>
+          <t>16494</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1851; 11183</t>
+          <t>1874; 10712</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9172; 27625</t>
+          <t>8810; 26198</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6862; 23041</t>
+          <t>6419; 22085</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1533; 13366</t>
+          <t>1378; 14721</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5767; 19726</t>
+          <t>5163; 18106</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3085; 16502</t>
+          <t>3639; 17159</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3888; 16253</t>
+          <t>4617; 15526</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5008; 19498</t>
+          <t>5445; 18945</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9011; 25719</t>
+          <t>9020; 24187</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14585; 35273</t>
+          <t>15303; 37198</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13570; 33310</t>
+          <t>13700; 32996</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8812; 26685</t>
+          <t>9326; 27353</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26660</t>
+          <t>31453</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6906</t>
+          <t>11360</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>33567</t>
+          <t>42812</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18852; 40520</t>
+          <t>18040; 39557</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>29004; 54543</t>
+          <t>27645; 55186</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20425; 44863</t>
+          <t>20155; 43345</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17721; 38588</t>
+          <t>20941; 44750</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>16693; 36602</t>
+          <t>15813; 36926</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18616; 39012</t>
+          <t>18252; 38679</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10485; 27075</t>
+          <t>11311; 26739</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3829; 11952</t>
+          <t>6821; 18301</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>39073; 67276</t>
+          <t>40317; 70121</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>53097; 84366</t>
+          <t>53094; 86279</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>35756; 63339</t>
+          <t>37030; 66135</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>23492; 46770</t>
+          <t>30990; 57646</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>86878</t>
+          <t>96362</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>73690</t>
+          <t>73722</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>160567</t>
+          <t>170084</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>41142; 68425</t>
+          <t>40001; 69096</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>43123; 74170</t>
+          <t>41952; 71286</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>49961; 82046</t>
+          <t>51765; 81698</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>38838; 129383</t>
+          <t>78558; 118449</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>31944; 55680</t>
+          <t>31101; 54230</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>60216; 96339</t>
+          <t>60092; 94166</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>54989; 85678</t>
+          <t>55186; 86010</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>58013; 91628</t>
+          <t>62159; 87777</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>77898; 115898</t>
+          <t>78082; 116673</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>110894; 155840</t>
+          <t>110888; 155756</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>111687; 156272</t>
+          <t>113997; 157548</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>93922; 198638</t>
+          <t>147990; 194386</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>132761</t>
+          <t>139397</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>135509</t>
+          <t>151637</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>268270</t>
+          <t>291034</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>55222; 84197</t>
+          <t>54314; 85754</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>67373; 100848</t>
+          <t>67594; 102144</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>79150; 116054</t>
+          <t>77658; 115797</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>115947; 154149</t>
+          <t>120164; 159702</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>70590; 104163</t>
+          <t>67937; 101232</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>97643; 135455</t>
+          <t>96379; 135386</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98889; 142215</t>
+          <t>100261; 139483</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>121247; 150244</t>
+          <t>134992; 169855</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>133176; 175631</t>
+          <t>134198; 179157</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>173346; 224210</t>
+          <t>173638; 224916</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>188271; 241147</t>
+          <t>184810; 240320</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>245491; 292938</t>
+          <t>266807; 319057</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>110601</t>
+          <t>120897</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>346632</t>
+          <t>154635</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>457233</t>
+          <t>275532</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>45818; 72490</t>
+          <t>45042; 70694</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>95605; 130901</t>
+          <t>95420; 131733</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>88157; 121549</t>
+          <t>89470; 122459</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>96048; 124447</t>
+          <t>104909; 135493</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>80749; 112749</t>
+          <t>80959; 113566</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>105876; 140779</t>
+          <t>105399; 142913</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>100252; 137838</t>
+          <t>99479; 135524</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>207137; 503280</t>
+          <t>140890; 169276</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>132427; 174425</t>
+          <t>135074; 173504</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>212063; 265665</t>
+          <t>210061; 262523</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>200250; 249791</t>
+          <t>199671; 247526</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>313267; 706859</t>
+          <t>255484; 298423</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>102408</t>
+          <t>112566</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>178127</t>
+          <t>192206</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>280535</t>
+          <t>304773</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>33622; 56774</t>
+          <t>32928; 56705</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>66621; 100356</t>
+          <t>66511; 98782</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>67258; 94251</t>
+          <t>67898; 93517</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>90492; 116205</t>
+          <t>98457; 126302</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>69635; 104260</t>
+          <t>70465; 105180</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>118614; 158760</t>
+          <t>118643; 156449</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>114459; 157074</t>
+          <t>115690; 159530</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>165001; 191492</t>
+          <t>176915; 208297</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>111143; 150755</t>
+          <t>112496; 152966</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>194358; 241238</t>
+          <t>194771; 246045</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>192996; 241408</t>
+          <t>190994; 241323</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>261821; 300811</t>
+          <t>284522; 327170</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>464651</t>
+          <t>506606</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>756318</t>
+          <t>599485</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1220969</t>
+          <t>1106090</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>229997; 291763</t>
+          <t>227814; 290827</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>349516; 429276</t>
+          <t>351376; 433553</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>353501; 427026</t>
+          <t>353223; 424568</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>365988; 515380</t>
+          <t>468873; 550434</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>312640; 385338</t>
+          <t>312230; 383320</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>448403; 533428</t>
+          <t>446382; 532027</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>428803; 514035</t>
+          <t>427646; 514429</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>572572; 1282956</t>
+          <t>564001; 633319</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>561635; 658087</t>
+          <t>562402; 654366</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>822841; 934543</t>
+          <t>821373; 935342</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>802335; 915480</t>
+          <t>796559; 914997</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1019748; 1924356</t>
+          <t>1055483; 1159513</t>
         </is>
       </c>
     </row>
